--- a/Sedes_a_priorizar_Nasa_CxaCxa_2.xlsx
+++ b/Sedes_a_priorizar_Nasa_CxaCxa_2.xlsx
@@ -450,7 +450,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B2" t="n">
         <v>219517000169</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B3" t="n">
         <v>219517800009</v>
@@ -512,7 +512,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B4" t="n">
         <v>219517000045</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B5" t="n">
         <v>219517000568</v>
@@ -574,7 +574,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B6" t="n">
         <v>219517001076</v>
@@ -605,7 +605,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B7" t="n">
         <v>219517000550</v>
@@ -636,7 +636,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B8" t="n">
         <v>219517000720</v>
@@ -667,7 +667,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B9" t="n">
         <v>219517000151</v>
